--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR ATUADOR MARCHA LENTA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR ATUADOR MARCHA LENTA.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON CG TITAN FAN160 2018 A 2023 350501</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON CG TITAN FAN160 2018 A 2023 350501</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON BIZ125 2016 A 2023 350500</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON BIZ125 2016 A 2023 350500</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON CG TITAN  FAN160 2016 A 2017 350535</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON CG TITAN  FAN160 2016 A 2017 350535</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON NMAX160 2017 A 2020 350503</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON NMAX160 2017 A 2020 350503</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON ELITE125 2019 A 2023 350497</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON ELITE125 2019 A 2023 350497</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON NMAX160 2021 A 2022 350502</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON NMAX160 2021 A 2022 350502</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON BIZ125 2011 A 2015 350499</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON BIZ125 2011 A 2015 350499</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON PCX125 2014 A 2016/ PCX150 2015 A 2018 189048</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON PCX125 2014 A 2016/ PCX150 2015 A 2018 189048</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON PCX125 2014 A 2016/ PCX150 2015 A 2018 189048</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON PCX125 2014 A 2016/ PCX150 2015 A 2018 189048</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -657,7 +657,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -670,7 +674,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON TITAN CG150 2009 A 2015/ NXR150 2009 A 2014/ NXR160 2022/ XRE190 189053</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON TITAN CG150 2009 A 2015/ NXR150 2009 A 2014/ NXR160 2022/ XRE190 189053</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON YS150 FAZER/ FACTOR125/ XTZ150 189057</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON YS150 FAZER/ FACTOR125/ XTZ150 189057</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -703,7 +707,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -716,7 +724,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA IRON CB300 2010 A 2015/ XRE300 2010 A 2023/ CB250F TWISTER 189050</t>
+          <t>SENSOR ATUADOR MARCHA LENTA IRON CB300 2010 A 2015/ XRE300 2010 A 2023/ CB250F TWISTER 189050</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -741,7 +749,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SENSOR ATUA MARC LENTA MAGNETRON CG TITAN FAN 160 2018 A 2024 90225290</t>
+          <t>SENSOR ATUADOR MARCHA LENTA MAGNETRON CG TITAN FAN 160 2018 A 2024 90225290</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR ATUADOR MARCHA LENTA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR ATUADOR MARCHA LENTA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,11 +672,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -755,11 +690,6 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>165</t>
         </is>
       </c>
     </row>
